--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -875,13 +875,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45163.60900934813</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45238</v>
+      </c>
+    </row>
     <row r="6" ht="22.5" customHeight="1" s="16">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -952,16 +948,6 @@
       <c r="D13" s="44" t="n"/>
       <c r="E13" s="44" t="n"/>
     </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24">
       <c r="C24" s="18" t="n"/>
     </row>
@@ -1017,7 +1003,7 @@
       </c>
       <c r="C30" s="45" t="n"/>
       <c r="D30" s="28" t="n">
-        <v>863.639</v>
+        <v>993.1849999999999</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="16">
@@ -1033,7 +1019,7 @@
       </c>
       <c r="C31" s="45" t="n"/>
       <c r="D31" s="28" t="n">
-        <v>1022.661</v>
+        <v>1176.06</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="16">
@@ -1049,7 +1035,7 @@
       </c>
       <c r="C32" s="45" t="n"/>
       <c r="D32" s="28" t="n">
-        <v>1154.773</v>
+        <v>1327.989</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1" s="16">
@@ -1065,10 +1051,9 @@
       </c>
       <c r="C33" s="45" t="n"/>
       <c r="D33" s="28" t="n">
-        <v>1455.708</v>
-      </c>
-    </row>
-    <row r="34"/>
+        <v>1674.064</v>
+      </c>
+    </row>
     <row r="35" ht="18" customHeight="1" s="16">
       <c r="A35" s="36" t="n"/>
       <c r="B35" s="36" t="inlineStr">
@@ -1085,34 +1070,29 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="16"/>
     <row r="38" ht="16.5" customHeight="1" s="16"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="16">
       <c r="A42" s="6" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="4" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -1081,18 +1081,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45238</v>
+        <v>45239</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="16">
@@ -1081,18 +1081,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -1081,18 +1081,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45239</v>
+        <v>45244</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="16">

--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45244</v>
+        <v>45245</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="16">
@@ -1081,18 +1081,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45245</v>
+        <v>45251</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="16">

--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -1081,18 +1081,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45251</v>
+        <v>45253</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="16">

--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="16">
@@ -1081,18 +1081,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="16">
@@ -1081,18 +1081,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -875,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="16">

--- a/LISTAS/ma/pasador con portacerrojo.xlsx
+++ b/LISTAS/ma/pasador con portacerrojo.xlsx
@@ -875,9 +875,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="n">
-        <v>45266</v>
-      </c>
-    </row>
+        <v>45226.65155765408</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="16">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -948,6 +952,16 @@
       <c r="D13" s="44" t="n"/>
       <c r="E13" s="44" t="n"/>
     </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24">
       <c r="C24" s="18" t="n"/>
     </row>
@@ -1003,7 +1017,7 @@
       </c>
       <c r="C30" s="45" t="n"/>
       <c r="D30" s="28" t="n">
-        <v>993.1849999999999</v>
+        <v>1382.01</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="16">
@@ -1019,7 +1033,7 @@
       </c>
       <c r="C31" s="45" t="n"/>
       <c r="D31" s="28" t="n">
-        <v>1176.06</v>
+        <v>1636.48</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="16">
@@ -1035,7 +1049,7 @@
       </c>
       <c r="C32" s="45" t="n"/>
       <c r="D32" s="28" t="n">
-        <v>1327.989</v>
+        <v>1847.89</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1" s="16">
@@ -1051,9 +1065,10 @@
       </c>
       <c r="C33" s="45" t="n"/>
       <c r="D33" s="28" t="n">
-        <v>1674.064</v>
-      </c>
-    </row>
+        <v>2329.46</v>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="16">
       <c r="A35" s="36" t="n"/>
       <c r="B35" s="36" t="inlineStr">
@@ -1070,29 +1085,34 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="16"/>
     <row r="38" ht="16.5" customHeight="1" s="16"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="16">
       <c r="A42" s="6" t="n"/>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="4" t="n"/>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
